--- a/dance_registration_forms/050_dance_audition_form_template--dance_registration_forms.xlsx
+++ b/dance_registration_forms/050_dance_audition_form_template--dance_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -907,8 +907,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -936,12 +936,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'prefer_not_to_answer'}</t>
+          <t>prefer_not_to_answer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Prefer not to answer'}</t>
+          <t>Prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'am'}</t>
+          <t>am</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'AM'}</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'pm'}</t>
+          <t>pm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'PM'}</t>
+          <t>PM</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'all_day'}</t>
+          <t>all_day</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'All Day'}</t>
+          <t>All Day</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'ballet'}</t>
+          <t>ballet</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Ballet'}</t>
+          <t>Ballet</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'tap'}</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Tap'}</t>
+          <t>Tap</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'jazz'}</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Jazz'}</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'hip_hop'}</t>
+          <t>hip_hop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Hip Hop'}</t>
+          <t>Hip Hop</t>
         </is>
       </c>
     </row>
